--- a/data/trans_dic/P21D_5_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21D_5_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,26</t>
+          <t>0,25; 2,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,82</t>
+          <t>0,27; 1,89</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,82</t>
+          <t>0,09; 1,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,96</t>
+          <t>0,05; 1,0</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,25</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,54</t>
+          <t>0,04; 0,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,74</t>
+          <t>0,19; 0,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,48</t>
+          <t>0,16; 0,49</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4544</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2861</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3690</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2689</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4736</t>
+          <t>0; 5889</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4448</t>
+          <t>0; 5832</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1854</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4456</t>
+          <t>0; 3246</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3758</t>
+          <t>0; 3906</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6272</t>
+          <t>0; 8184</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4074</t>
+          <t>0; 4153</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7615</t>
+          <t>0; 7033</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6058</t>
+          <t>0; 5943</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>576; 5117</t>
+          <t>578; 5058</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1272; 8464</t>
+          <t>1274; 8792</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1235</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>163; 3381</t>
+          <t>162; 3304</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>161; 3292</t>
+          <t>162; 3405</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3120</t>
+          <t>0; 2810</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 946</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>0; 3595</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>789; 8912</t>
+          <t>698; 9228</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2884; 11779</t>
+          <t>2979; 11657</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4642; 15567</t>
+          <t>5164; 16093</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_5_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21D_5_R-Edad-trans_dic.xlsx
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,1; 1,13</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,23</t>
+          <t>0,24; 2,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,89</t>
+          <t>0,25; 1,67</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,78</t>
+          <t>0,19; 2,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,0</t>
+          <t>0,1; 1,21</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,25</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,55</t>
+          <t>0,06; 0,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,73</t>
+          <t>0,2; 0,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,49</t>
+          <t>0,17; 0,51</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>987</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>987</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5889</t>
+          <t>0; 5032</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5832</t>
+          <t>0; 4446</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>810</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>810</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3246</t>
+          <t>0; 4000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3906</t>
+          <t>0; 3562</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2512</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 8184</t>
+          <t>0; 6373</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4153</t>
+          <t>0; 4801</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7033</t>
+          <t>680; 7455</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3616</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5943</t>
+          <t>0; 6859</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>578; 5058</t>
+          <t>613; 5154</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1274; 8792</t>
+          <t>1279; 8544</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1553</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>162; 3304</t>
+          <t>384; 4244</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162; 3405</t>
+          <t>385; 4523</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 2810</t>
+          <t>0; 3182</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3595</t>
+          <t>0; 2938</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>698; 9228</t>
+          <t>989; 8574</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2979; 11657</t>
+          <t>3369; 12548</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5164; 16093</t>
+          <t>5702; 16740</t>
         </is>
       </c>
     </row>
